--- a/docs/station4/例外仕様書.xlsx
+++ b/docs/station4/例外仕様書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="11540"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t>例外コード</t>
   </si>
@@ -57,12 +57,7 @@
   </si>
   <si>
     <t>1.入力値の検証結果をログに出力
-2.入力ホームに戻る
-3.エラー箇所を赤枠で強調表示</t>
-  </si>
-  <si>
-    <t>入力内容に誤りがあります。
-赤枠の項目を確認してください。</t>
+2.エラー内容を画面に表示</t>
   </si>
   <si>
     <t>Warnig</t>
@@ -78,12 +73,12 @@
   </si>
   <si>
     <t>1.失敗回数をカウント
-2.1分間に3回失敗で、その後1分間は新たなログイン試行を受け付けない。
+2.3回失敗で、その後1分間は新たなログイン試行を受け付けない。
 3.アクセス元IPをログ記録</t>
   </si>
   <si>
-    <t>IDまたはパスワードが間違っています。
-（あと{n}かいで一時的にロックされます。）</t>
+    <t>「IDまたはパスワードが間違っています。」
+「ログイン試行の規定数に達しました。60秒後に再度お試しください。」</t>
   </si>
   <si>
     <t>E003</t>
@@ -105,6 +100,90 @@
   </si>
   <si>
     <t>Error</t>
+  </si>
+  <si>
+    <t>E004</t>
+  </si>
+  <si>
+    <t>NotFoundError</t>
+  </si>
+  <si>
+    <t>データが存在しない</t>
+  </si>
+  <si>
+    <t>1. エラーをログに記録
+2. 404画面へ遷移</t>
+  </si>
+  <si>
+    <t>指定されたページまたはデータが見つかりません。</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t>E005</t>
+  </si>
+  <si>
+    <t>ServerError</t>
+  </si>
+  <si>
+    <t>サーバー内部エラー</t>
+  </si>
+  <si>
+    <t>1. エラーログにスタックトレースを出力
+2. エラーページへ遷移</t>
+  </si>
+  <si>
+    <t>E006</t>
+  </si>
+  <si>
+    <t>DBError</t>
+  </si>
+  <si>
+    <t>データベース処理失敗</t>
+  </si>
+  <si>
+    <t>1. トランザクションをロールバック
+2. 詳細をログ出力
+3. 再試行不可に設定</t>
+  </si>
+  <si>
+    <t>データの保存に失敗しました。
+再度お試しください。</t>
+  </si>
+  <si>
+    <t>E007</t>
+  </si>
+  <si>
+    <t>UploadError</t>
+  </si>
+  <si>
+    <t>ファイル／画像アップロード失敗</t>
+  </si>
+  <si>
+    <t>1. サイズ・形式を検証
+2. 不正時はアップロードを中断
+3. ログに詳細出力</t>
+  </si>
+  <si>
+    <t>ファイルのアップロードに失敗しました。
+形式またはサイズを確認してください。</t>
+  </si>
+  <si>
+    <t>E008</t>
+  </si>
+  <si>
+    <t>TokenExpired</t>
+  </si>
+  <si>
+    <t>トークンの期限切れ</t>
+  </si>
+  <si>
+    <t>1.ログアウト → メッセージ表示
+2.ログイン画面へ遷移</t>
+  </si>
+  <si>
+    <t>ログインの有効期限が切れました</t>
   </si>
 </sst>
 </file>
@@ -743,12 +822,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1286,14 +1368,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.7692307692308" customWidth="1"/>
     <col min="2" max="2" width="17.6153846153846" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="32.5" customWidth="1"/>
-    <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="5" max="5" width="56.3846153846154" customWidth="1"/>
     <col min="6" max="6" width="15.1538461538462" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1317,7 +1399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="51" spans="1:6">
+    <row r="2" ht="34" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1330,51 +1412,149 @@
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" ht="84" spans="1:6">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" ht="51" spans="1:6">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="5" ht="34" spans="1:6">
+      <c r="A5" t="s">
         <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="51" spans="1:6">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="68" spans="1:6">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="51" spans="1:6">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1" spans="1:6">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
